--- a/data/trans_orig/P6607-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6607-Clase-trans_orig.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W39"/>
+  <dimension ref="A1:W34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2012</t>
+          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2012 (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>130896</t>
+          <t>133052</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>168282</t>
+          <t>169382</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>124078</t>
+          <t>123280</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>149832</t>
+          <t>148784</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>264484</t>
+          <t>265517</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>308313</t>
+          <t>309116</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,59%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68075</t>
+          <t>68137</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101264</t>
+          <t>99580</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33935</t>
+          <t>34552</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57564</t>
+          <t>59196</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110408</t>
+          <t>109820</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150217</t>
+          <t>148805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,13%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32210</t>
+          <t>33485</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57291</t>
+          <t>58612</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>16630</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39032</t>
+          <t>39455</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67360</t>
+          <t>69200</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15186</t>
+          <t>15206</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34882</t>
+          <t>35669</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6229</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15868</t>
+          <t>16324</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37769</t>
+          <t>36201</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>106652</t>
+          <t>106033</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>140784</t>
+          <t>139302</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>131488</t>
+          <t>131202</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>150981</t>
+          <t>150102</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>243714</t>
+          <t>243276</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>286109</t>
+          <t>286889</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>68,11%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25274</t>
+          <t>25892</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>51498</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18307</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35009</t>
+          <t>34280</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61637</t>
+          <t>61536</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>46292</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75527</t>
+          <t>73516</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15854</t>
+          <t>15561</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51474</t>
+          <t>51593</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84569</t>
+          <t>84817</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,14%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25091</t>
+          <t>24578</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47097</t>
+          <t>47502</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30297</t>
+          <t>30554</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>56832</t>
+          <t>58441</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101907</t>
+          <t>100597</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>134587</t>
+          <t>133843</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83426</t>
+          <t>82530</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>99376</t>
+          <t>99247</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>190074</t>
+          <t>191102</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>228611</t>
+          <t>228448</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,39%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67536</t>
+          <t>67520</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>97792</t>
+          <t>95752</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17894</t>
+          <t>18863</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>75822</t>
+          <t>76255</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>109598</t>
+          <t>108547</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36751</t>
+          <t>35852</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60672</t>
+          <t>60231</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9459</t>
+          <t>10558</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39742</t>
+          <t>40346</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64825</t>
+          <t>65773</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22863</t>
+          <t>22950</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46675</t>
+          <t>48001</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11044</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27017</t>
+          <t>27060</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52518</t>
+          <t>52624</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>139401</t>
+          <t>141318</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>181278</t>
+          <t>181667</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>206049</t>
+          <t>206478</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>237210</t>
+          <t>238633</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>354895</t>
+          <t>356107</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>412275</t>
+          <t>411953</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,92%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61966</t>
+          <t>61801</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>95621</t>
+          <t>95608</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37984</t>
+          <t>36648</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63562</t>
+          <t>63276</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105610</t>
+          <t>105128</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>150451</t>
+          <t>148428</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>62163</t>
+          <t>64014</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>94727</t>
+          <t>98256</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>21486</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>74028</t>
+          <t>74629</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>110847</t>
+          <t>110232</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>89243</t>
+          <t>90870</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>127135</t>
+          <t>126161</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24521</t>
+          <t>25469</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>102473</t>
+          <t>103223</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>143329</t>
+          <t>143932</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>17626</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36323</t>
+          <t>36971</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>82928</t>
+          <t>82904</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>109439</t>
+          <t>111040</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>103204</t>
+          <t>106886</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>142540</t>
+          <t>141710</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,14%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>12635</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31915</t>
+          <t>32112</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25671</t>
+          <t>25801</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46920</t>
+          <t>48439</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43315</t>
+          <t>43145</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71227</t>
+          <t>72239</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21628</t>
+          <t>22411</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42615</t>
+          <t>42925</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12091</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28745</t>
+          <t>27660</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>37649</t>
+          <t>38354</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>64452</t>
+          <t>65082</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>62609</t>
+          <t>60915</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>86852</t>
+          <t>86532</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>15698</t>
+          <t>15905</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>36849</t>
+          <t>35791</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>81392</t>
+          <t>81886</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>117090</t>
+          <t>118236</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,99%</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3567,107 +3567,107 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>541</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>578236</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>540046</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>615807</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>639</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>690546</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>659481</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>716899</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1268782</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1216760</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1316405</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,81%</t>
         </is>
       </c>
     </row>
@@ -3680,107 +3680,107 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>284</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>298429</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>268030</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>332366</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>141</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>151411</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129340</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>175282</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>425</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>449840</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>410417</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>488004</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -3793,107 +3793,107 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>248</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>260847</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>234360</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>293645</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50704</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37145</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67265</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>294</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>311551</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>279964</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>347201</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -3906,107 +3906,107 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>255</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>274563</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>244837</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>307204</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53829</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40413</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>69093</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>328392</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>289413</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>360075</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -4019,690 +4019,120 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1412074</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1412074</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1412074</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>874</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>946490</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>946490</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>946490</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2358564</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2358564</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2358564</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>541</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>578236</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>539460</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>613819</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>40,95%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>38,2%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>43,47%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>690546</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>661766</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>718364</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>72,96%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>69,92%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>75,9%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>1180</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>1268782</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>1214727</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>1317617</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>53,79%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>51,5%</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>55,87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n"/>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Algunas veces</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>298429</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>266271</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>332619</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>21,13%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>18,86%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>23,56%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>151411</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>130074</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>176825</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>16,0%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>13,74%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>18,68%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>425</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>449840</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>410354</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>489697</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>19,07%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>17,4%</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>20,76%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n"/>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Muchas veces</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>260847</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>231578</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>291893</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>18,47%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>16,4%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>20,67%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>50704</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>37366</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>68036</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>7,19%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>311551</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>279821</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>347372</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>14,73%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n"/>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Siempre</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>274563</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>246765</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>304392</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>19,44%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>17,48%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>21,56%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>53829</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>40806</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>70279</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>7,43%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>328392</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>292255</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>362058</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>13,92%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>12,39%</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>15,35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n"/>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>1412074</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>1412074</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>1412074</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>874</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>946490</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>946490</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>946490</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>2202</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>2358564</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>2358564</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>2358564</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
-    <mergeCell ref="A34:A38"/>
     <mergeCell ref="A29:A33"/>
     <mergeCell ref="A9:A13"/>
     <mergeCell ref="A24:A28"/>
@@ -4723,7 +4153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W39"/>
+  <dimension ref="A1:W34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4754,7 +4184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2016</t>
+          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4949,12 +4379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>136504</t>
+          <t>137657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>172346</t>
+          <t>172117</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4964,12 +4394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4984,12 +4414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>137148</t>
+          <t>135434</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>163814</t>
+          <t>163516</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4999,12 +4429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5019,12 +4449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>283640</t>
+          <t>286625</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>328066</t>
+          <t>327859</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5034,12 +4464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,57%</t>
         </is>
       </c>
     </row>
@@ -5062,12 +4492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67228</t>
+          <t>68594</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101472</t>
+          <t>100316</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5077,12 +4507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5097,12 +4527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32822</t>
+          <t>32127</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55789</t>
+          <t>56677</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5112,12 +4542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5132,12 +4562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107092</t>
+          <t>107989</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>147327</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5147,12 +4577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,55%</t>
         </is>
       </c>
     </row>
@@ -5175,12 +4605,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18485</t>
+          <t>19162</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5190,12 +4620,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5210,12 +4640,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22326</t>
+          <t>21506</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5225,12 +4655,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5245,12 +4675,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29891</t>
+          <t>27777</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53332</t>
+          <t>53629</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5260,12 +4690,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -5288,12 +4718,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22081</t>
+          <t>22574</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5303,12 +4733,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5323,12 +4753,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14463</t>
+          <t>12657</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5338,12 +4768,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5358,12 +4788,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11173</t>
+          <t>11627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29586</t>
+          <t>30076</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5373,12 +4803,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -5518,12 +4948,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>95904</t>
+          <t>93434</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>127821</t>
+          <t>124710</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5533,12 +4963,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5553,12 +4983,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>121131</t>
+          <t>121973</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>147314</t>
+          <t>147050</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5568,12 +4998,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5588,12 +5018,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>226181</t>
+          <t>226053</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>266238</t>
+          <t>265271</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5603,12 +5033,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,61%</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5061,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35247</t>
+          <t>35509</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58600</t>
+          <t>60779</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5646,12 +5076,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5666,12 +5096,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21737</t>
+          <t>22006</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43305</t>
+          <t>43225</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5681,12 +5111,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5701,12 +5131,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64626</t>
+          <t>62692</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97454</t>
+          <t>96260</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5716,12 +5146,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5174,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33760</t>
+          <t>33979</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60060</t>
+          <t>59058</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5759,12 +5189,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5779,12 +5209,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8532</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23718</t>
+          <t>23183</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5794,12 +5224,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5814,12 +5244,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45700</t>
+          <t>48284</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75526</t>
+          <t>77036</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5829,12 +5259,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5287,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26869</t>
+          <t>27493</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51346</t>
+          <t>51565</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5872,12 +5302,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5892,12 +5322,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15947</t>
+          <t>16194</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5907,12 +5337,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5927,12 +5357,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34038</t>
+          <t>34003</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60720</t>
+          <t>60623</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5942,12 +5372,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -6087,12 +5517,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64281</t>
+          <t>64833</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92352</t>
+          <t>91856</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6102,12 +5532,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6122,12 +5552,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51703</t>
+          <t>51632</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62827</t>
+          <t>62589</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6137,12 +5567,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6157,12 +5587,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118375</t>
+          <t>119044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153570</t>
+          <t>154028</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6172,12 +5602,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,45%</t>
         </is>
       </c>
     </row>
@@ -6200,12 +5630,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63817</t>
+          <t>64219</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93024</t>
+          <t>91650</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6215,12 +5645,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6235,12 +5665,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2693</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13322</t>
+          <t>13637</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6250,12 +5680,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6270,12 +5700,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>69113</t>
+          <t>69785</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>102529</t>
+          <t>101308</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6285,12 +5715,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -6313,12 +5743,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29027</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>52235</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6328,12 +5758,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6353,7 +5783,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6368,7 +5798,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6383,12 +5813,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29767</t>
+          <t>30661</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55080</t>
+          <t>55649</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6398,12 +5828,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -6426,12 +5856,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11852</t>
+          <t>12167</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29992</t>
+          <t>29950</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6441,12 +5871,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6461,12 +5891,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6476,12 +5906,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6496,12 +5926,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11873</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30451</t>
+          <t>31349</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6511,12 +5941,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -6656,12 +6086,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>147458</t>
+          <t>146998</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>188158</t>
+          <t>188993</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6671,12 +6101,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6691,12 +6121,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>244225</t>
+          <t>243100</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>277926</t>
+          <t>278288</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6706,12 +6136,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6726,12 +6156,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>402992</t>
+          <t>398979</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>460464</t>
+          <t>461633</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6741,12 +6171,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,28%</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6199,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>102744</t>
+          <t>103306</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>142423</t>
+          <t>140772</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6784,12 +6214,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6804,12 +6234,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55283</t>
+          <t>55641</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>85212</t>
+          <t>85694</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6819,12 +6249,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6839,12 +6269,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>164680</t>
+          <t>166849</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216115</t>
+          <t>216122</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6854,7 +6284,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6882,12 +6312,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>63320</t>
+          <t>64088</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>95802</t>
+          <t>97149</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6897,12 +6327,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6917,12 +6347,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19299</t>
+          <t>18886</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39350</t>
+          <t>38542</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6932,12 +6362,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6952,12 +6382,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>88540</t>
+          <t>87970</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>127196</t>
+          <t>126294</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6967,12 +6397,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>97329</t>
+          <t>95817</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>132097</t>
+          <t>134007</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7010,12 +6440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7030,12 +6460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17724</t>
+          <t>18818</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7045,12 +6475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7065,12 +6495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>104276</t>
+          <t>104967</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>147557</t>
+          <t>147224</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7080,12 +6510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +6655,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23461</t>
+          <t>23869</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45093</t>
+          <t>45475</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7240,12 +6670,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7260,12 +6690,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>99051</t>
+          <t>98623</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>127555</t>
+          <t>125926</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7275,12 +6705,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7295,12 +6725,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>128181</t>
+          <t>128742</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>164855</t>
+          <t>167886</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7310,12 +6740,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -7338,12 +6768,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21664</t>
+          <t>21298</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42657</t>
+          <t>42721</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7353,12 +6783,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7373,12 +6803,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31926</t>
+          <t>31129</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>54278</t>
+          <t>55109</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7388,12 +6818,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7408,12 +6838,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>58751</t>
+          <t>58245</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>89079</t>
+          <t>90123</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7423,12 +6853,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -7451,12 +6881,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26981</t>
+          <t>26539</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50235</t>
+          <t>49311</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7466,12 +6896,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7486,12 +6916,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>13796</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7501,12 +6931,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7521,12 +6951,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>32744</t>
+          <t>32380</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>57471</t>
+          <t>58600</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7536,12 +6966,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -7564,12 +6994,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>77490</t>
+          <t>78024</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>106725</t>
+          <t>107432</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7579,12 +7009,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7599,12 +7029,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>23938</t>
+          <t>24122</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>44700</t>
+          <t>44733</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7614,12 +7044,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7634,12 +7064,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>106739</t>
+          <t>105539</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>145753</t>
+          <t>144438</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7649,12 +7079,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,06%</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7204,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -7784,107 +7214,107 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>514</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>545508</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>508040</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>581427</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>703</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>719217</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>687389</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>747544</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1264725</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1214686</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1313503</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,7%</t>
         </is>
       </c>
     </row>
@@ -7897,107 +7327,107 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>332</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>362042</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>328787</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>395988</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>185</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>191882</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>168571</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>218958</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>517</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>553924</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>516673</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>600616</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -8010,107 +7440,107 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>210</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>227972</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>201614</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>259652</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64201</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50442</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>80990</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>274</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>292173</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>257927</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>323034</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -8123,107 +7553,107 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>258</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>276320</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>248389</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>308930</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59041</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45448</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75365</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>316</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>335362</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>303342</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>370961</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -8236,690 +7666,120 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1411843</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1411843</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1411843</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1034341</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1034341</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1034341</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2446184</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2446184</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2446184</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>545508</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>506671</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>584108</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>38,64%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>35,89%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>41,37%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>703</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>719217</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>689514</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>745010</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>69,53%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>66,66%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>72,03%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>1217</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>1264725</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>1212697</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>1310893</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>51,7%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>49,58%</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>53,59%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n"/>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Algunas veces</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>362042</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>325486</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>396758</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>25,64%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>23,05%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>28,1%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>191882</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>170227</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>218871</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>18,55%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>16,46%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>21,16%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>553924</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>509049</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>594474</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>22,64%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>20,81%</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>24,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n"/>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Muchas veces</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>227972</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>199267</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>259207</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>16,15%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>14,11%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>18,36%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>64201</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>50626</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>80508</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>6,21%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>292173</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>259594</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>323038</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>11,94%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>10,61%</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n"/>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Siempre</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>276320</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>247712</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>311315</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>19,57%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>22,05%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>59041</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>46018</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>76428</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>7,39%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>335362</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>298795</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>369379</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>13,71%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>12,21%</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>15,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n"/>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>1314</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>1411843</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>1411843</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>1411843</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>1010</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>1034341</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>1034341</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>1034341</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>2324</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>2446184</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>2446184</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>2446184</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
-    <mergeCell ref="A34:A38"/>
     <mergeCell ref="A29:A33"/>
     <mergeCell ref="A9:A13"/>
     <mergeCell ref="A24:A28"/>
@@ -8940,7 +7800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W39"/>
+  <dimension ref="A1:W34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8971,7 +7831,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2023</t>
+          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9166,12 +8026,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>105024</t>
+          <t>105637</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>132929</t>
+          <t>131843</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9181,12 +8041,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9201,12 +8061,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>117789</t>
+          <t>117268</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>133437</t>
+          <t>133665</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9216,12 +8076,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9236,12 +8096,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>227441</t>
+          <t>229823</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>260267</t>
+          <t>260344</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9251,12 +8111,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,78%</t>
         </is>
       </c>
     </row>
@@ -9279,12 +8139,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21620</t>
+          <t>21321</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42246</t>
+          <t>41591</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9294,12 +8154,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9314,12 +8174,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12091</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26377</t>
+          <t>27098</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9329,12 +8189,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9349,12 +8209,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38129</t>
+          <t>38336</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61349</t>
+          <t>62309</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9364,12 +8224,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +8252,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>14556</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36325</t>
+          <t>36310</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9407,12 +8267,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9427,12 +8287,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9442,12 +8302,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9462,12 +8322,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>18061</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42028</t>
+          <t>43117</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9477,12 +8337,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +8365,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>13357</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9520,12 +8380,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9540,12 +8400,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6471</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9555,12 +8415,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9575,12 +8435,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15514</t>
+          <t>15962</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9590,12 +8450,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -9735,12 +8595,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85411</t>
+          <t>86050</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>113271</t>
+          <t>112653</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9750,12 +8610,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9770,12 +8630,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89262</t>
+          <t>89089</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>103638</t>
+          <t>103183</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9785,12 +8645,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9805,12 +8665,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>182227</t>
+          <t>181439</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>212373</t>
+          <t>213201</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9820,12 +8680,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>
@@ -9848,12 +8708,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23854</t>
+          <t>25315</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47689</t>
+          <t>48471</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9863,12 +8723,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9883,12 +8743,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18709</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9898,12 +8758,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9918,12 +8778,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33079</t>
+          <t>34602</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58947</t>
+          <t>60913</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9933,12 +8793,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +8821,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5895</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20130</t>
+          <t>20013</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9976,12 +8836,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9996,12 +8856,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>10437</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10011,12 +8871,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10031,12 +8891,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10698</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27429</t>
+          <t>28510</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10046,12 +8906,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +8934,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>5685</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22755</t>
+          <t>23196</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10089,12 +8949,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10109,12 +8969,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>314</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10124,12 +8984,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10144,12 +9004,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25697</t>
+          <t>25037</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10159,12 +9019,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -10304,12 +9164,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10085</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131880</t>
+          <t>129755</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10319,12 +9179,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10339,12 +9199,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36345</t>
+          <t>36234</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42830</t>
+          <t>42654</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10354,12 +9214,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10374,12 +9234,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19341</t>
+          <t>21374</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>205299</t>
+          <t>208241</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10389,12 +9249,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
@@ -10417,12 +9277,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>13129</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>148041</t>
+          <t>149368</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10432,12 +9292,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10452,12 +9312,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1633</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10467,12 +9327,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10487,12 +9347,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>14663</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>135433</t>
+          <t>133911</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10502,12 +9362,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -10530,12 +9390,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63417</t>
+          <t>64044</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10545,12 +9405,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10570,7 +9430,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10585,7 +9445,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10600,12 +9460,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54504</t>
+          <t>51573</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10615,12 +9475,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -10643,12 +9503,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50057</t>
+          <t>49734</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>347114</t>
+          <t>342315</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10658,12 +9518,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10678,12 +9538,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10693,12 +9553,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10713,12 +9573,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39746</t>
+          <t>42533</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>380420</t>
+          <t>376766</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10728,12 +9588,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,3%</t>
         </is>
       </c>
     </row>
@@ -10873,12 +9733,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63996</t>
+          <t>63083</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96279</t>
+          <t>95519</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10888,12 +9748,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10908,12 +9768,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>126098</t>
+          <t>128752</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>150315</t>
+          <t>151370</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10923,12 +9783,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10943,12 +9803,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>196958</t>
+          <t>197771</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>242233</t>
+          <t>241373</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10958,12 +9818,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,8%</t>
         </is>
       </c>
     </row>
@@ -10986,12 +9846,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44970</t>
+          <t>44313</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>74562</t>
+          <t>75527</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11001,12 +9861,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11021,12 +9881,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26098</t>
+          <t>25911</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46178</t>
+          <t>45750</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11036,12 +9896,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11056,12 +9916,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>75516</t>
+          <t>77797</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>113443</t>
+          <t>112602</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11071,12 +9931,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -11099,12 +9959,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>48364</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>76477</t>
+          <t>78807</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11114,12 +9974,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11134,12 +9994,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8684</t>
+          <t>8868</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22718</t>
+          <t>22872</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11149,12 +10009,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11169,12 +10029,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>59613</t>
+          <t>60209</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>92593</t>
+          <t>93019</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11184,12 +10044,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -11212,12 +10072,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46188</t>
+          <t>46327</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>75572</t>
+          <t>76685</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11227,12 +10087,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11247,12 +10107,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>15873</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11267,7 +10127,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11282,12 +10142,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53544</t>
+          <t>55037</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87260</t>
+          <t>88764</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11297,12 +10157,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -11442,12 +10302,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12945</t>
+          <t>12935</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31796</t>
+          <t>32419</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11457,12 +10317,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11477,12 +10337,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29183</t>
+          <t>28388</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>75406</t>
+          <t>74724</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11492,12 +10352,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11512,12 +10372,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>52179</t>
+          <t>53022</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>94815</t>
+          <t>95589</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11527,12 +10387,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -11555,12 +10415,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23790</t>
+          <t>25328</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47150</t>
+          <t>48060</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11570,12 +10430,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11590,12 +10450,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39498</t>
+          <t>39680</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112295</t>
+          <t>112188</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11605,12 +10465,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11625,12 +10485,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>71023</t>
+          <t>72409</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>168693</t>
+          <t>161380</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11640,12 +10500,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>54,68%</t>
         </is>
       </c>
     </row>
@@ -11668,12 +10528,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10489</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27554</t>
+          <t>27057</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11683,12 +10543,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11703,12 +10563,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16017</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11723,7 +10583,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11738,12 +10598,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17442</t>
+          <t>17564</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>39439</t>
+          <t>37869</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11753,12 +10613,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -11781,12 +10641,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>45988</t>
+          <t>45539</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>72760</t>
+          <t>71375</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11796,12 +10656,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11816,12 +10676,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13782</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>40436</t>
+          <t>41843</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11831,12 +10691,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11851,12 +10711,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>59126</t>
+          <t>58639</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>108357</t>
+          <t>108441</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11866,12 +10726,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -11991,7 +10851,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -12001,107 +10861,107 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>340</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>360616</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>188940</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>481466</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>677</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>460666</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>372396</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>492107</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>821282</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>504900</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>971517</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,7%</t>
         </is>
       </c>
     </row>
@@ -12114,107 +10974,107 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>201</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>206826</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>105082</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>276703</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>156</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135550</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101242</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>248063</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>357</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>342375</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>207777</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>424860</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -12227,107 +11087,107 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>124</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133041</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66034</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>180150</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33687</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24651</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45487</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>174</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166728</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>104925</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>204631</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -12340,107 +11200,107 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>156</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>402758</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>189774</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>738814</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42796</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31775</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55762</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>219</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>445554</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>221966</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>960398</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,08%</t>
         </is>
       </c>
     </row>
@@ -12453,690 +11313,120 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>821</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1103241</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1103241</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1103241</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>946</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>672699</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>672699</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>672699</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1775939</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1775939</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1775939</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>360616</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>170540</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>474693</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>32,69%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>15,46%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>43,03%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>460666</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>391923</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>491231</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>68,48%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>58,26%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>73,02%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>821282</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>509889</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>978953</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>46,24%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>28,71%</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>55,12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n"/>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Algunas veces</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>206826</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>97655</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>279129</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>18,75%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>8,85%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>25,3%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>135550</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>102012</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>211811</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>20,15%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>15,16%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>31,49%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>342375</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>224863</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>424098</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>19,28%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>12,66%</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>23,88%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n"/>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Muchas veces</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>58565</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>179612</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>12,06%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>16,28%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>33687</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>23972</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>43428</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>166728</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>102763</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>210724</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>9,39%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>5,79%</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>11,87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n"/>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Siempre</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>402758</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>192931</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>772519</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>36,51%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>17,49%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>70,02%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>42796</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>32383</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>57266</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>8,51%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>445554</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>219425</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>956586</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>25,09%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>12,36%</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>53,86%</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n"/>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>1103241</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>1103241</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>1103241</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>672699</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>672699</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>672699</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>1767</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>1775939</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>1775939</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>1775939</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
-    <mergeCell ref="A34:A38"/>
     <mergeCell ref="A29:A33"/>
     <mergeCell ref="A9:A13"/>
     <mergeCell ref="A24:A28"/>

--- a/data/trans_orig/P6607-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6607-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>133052</t>
+          <t>131931</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>169382</t>
+          <t>169163</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>123280</t>
+          <t>123647</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>148784</t>
+          <t>149358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>265517</t>
+          <t>265121</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>309116</t>
+          <t>309109</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68137</t>
+          <t>67305</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99580</t>
+          <t>101259</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34552</t>
+          <t>34985</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59196</t>
+          <t>58619</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109820</t>
+          <t>109830</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148805</t>
+          <t>149131</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33485</t>
+          <t>31221</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58612</t>
+          <t>57760</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16630</t>
+          <t>17653</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39455</t>
+          <t>39536</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69200</t>
+          <t>68601</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>14551</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35669</t>
+          <t>33614</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>16170</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36201</t>
+          <t>36556</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>106033</t>
+          <t>106000</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>139302</t>
+          <t>139352</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>131202</t>
+          <t>130255</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>150102</t>
+          <t>150771</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>243276</t>
+          <t>242435</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>286889</t>
+          <t>286042</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,91%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25892</t>
+          <t>26054</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51498</t>
+          <t>51539</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18601</t>
+          <t>18751</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34280</t>
+          <t>34445</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61536</t>
+          <t>62732</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46292</t>
+          <t>47068</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73516</t>
+          <t>75073</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15561</t>
+          <t>15819</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51593</t>
+          <t>52283</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84817</t>
+          <t>82888</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24578</t>
+          <t>24259</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47502</t>
+          <t>49626</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16123</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30554</t>
+          <t>31382</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>58201</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100597</t>
+          <t>101834</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>133843</t>
+          <t>133377</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82530</t>
+          <t>84141</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>99247</t>
+          <t>99918</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>191102</t>
+          <t>189972</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>228448</t>
+          <t>228806</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,48%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67520</t>
+          <t>65802</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>95752</t>
+          <t>95748</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5297</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18863</t>
+          <t>17654</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>76255</t>
+          <t>76167</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>108547</t>
+          <t>108587</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35852</t>
+          <t>36210</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60231</t>
+          <t>60352</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10558</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40346</t>
+          <t>38836</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65773</t>
+          <t>65228</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22950</t>
+          <t>24496</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48001</t>
+          <t>46728</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10689</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27060</t>
+          <t>27434</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52624</t>
+          <t>52737</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>141318</t>
+          <t>140797</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>181667</t>
+          <t>182050</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>206478</t>
+          <t>206908</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>238633</t>
+          <t>237056</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>356107</t>
+          <t>357842</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>411953</t>
+          <t>411237</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,82%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61801</t>
+          <t>61861</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>95608</t>
+          <t>95435</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36648</t>
+          <t>37421</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63276</t>
+          <t>63139</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105128</t>
+          <t>104781</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>148428</t>
+          <t>148208</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>64014</t>
+          <t>63384</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>98256</t>
+          <t>97141</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21486</t>
+          <t>22098</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>74629</t>
+          <t>73227</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>110232</t>
+          <t>109291</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>90870</t>
+          <t>89190</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>126161</t>
+          <t>127856</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25469</t>
+          <t>25581</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>103223</t>
+          <t>102119</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>143932</t>
+          <t>144814</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17626</t>
+          <t>18362</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36971</t>
+          <t>38107</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>82904</t>
+          <t>83188</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>111040</t>
+          <t>109599</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>106886</t>
+          <t>105600</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>141710</t>
+          <t>142922</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,5%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>12496</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32112</t>
+          <t>30763</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25801</t>
+          <t>25382</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48439</t>
+          <t>46957</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43145</t>
+          <t>43679</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>72239</t>
+          <t>71924</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>21818</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42925</t>
+          <t>42934</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>12003</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>28227</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38354</t>
+          <t>37810</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>65082</t>
+          <t>64785</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>60915</t>
+          <t>62279</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>86532</t>
+          <t>87451</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>15905</t>
+          <t>15367</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>35791</t>
+          <t>35516</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>81886</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>118236</t>
+          <t>116860</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,57%</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>540046</t>
+          <t>541129</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>615807</t>
+          <t>614118</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>659481</t>
+          <t>660305</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>716899</t>
+          <t>715033</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1216760</t>
+          <t>1216187</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1316405</t>
+          <t>1316115</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,8%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>268030</t>
+          <t>266271</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>332366</t>
+          <t>333099</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>129340</t>
+          <t>129885</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>175282</t>
+          <t>174736</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>410417</t>
+          <t>408509</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>488004</t>
+          <t>489544</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>234360</t>
+          <t>231893</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>293645</t>
+          <t>291650</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>37145</t>
+          <t>37633</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>67265</t>
+          <t>67307</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>279964</t>
+          <t>282063</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>347201</t>
+          <t>348803</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>244837</t>
+          <t>241382</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>307204</t>
+          <t>306903</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>40413</t>
+          <t>40082</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>69093</t>
+          <t>70524</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>289413</t>
+          <t>294535</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>360075</t>
+          <t>360604</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137657</t>
+          <t>138979</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>172117</t>
+          <t>172605</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>135434</t>
+          <t>137685</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>163516</t>
+          <t>164040</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>286625</t>
+          <t>284018</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>327859</t>
+          <t>328652</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,73%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68594</t>
+          <t>68323</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100316</t>
+          <t>98930</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32127</t>
+          <t>33361</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56677</t>
+          <t>57891</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107989</t>
+          <t>106838</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145518</t>
+          <t>146972</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,84%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19162</t>
+          <t>18771</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>38966</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21506</t>
+          <t>21527</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27777</t>
+          <t>28732</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53629</t>
+          <t>53553</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22574</t>
+          <t>21677</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12657</t>
+          <t>13558</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11627</t>
+          <t>11945</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30076</t>
+          <t>30023</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>93434</t>
+          <t>94772</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>124710</t>
+          <t>126230</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>121973</t>
+          <t>121941</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>147050</t>
+          <t>146671</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>226053</t>
+          <t>223261</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>265271</t>
+          <t>264752</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,49%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35509</t>
+          <t>35408</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60779</t>
+          <t>60399</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22006</t>
+          <t>21548</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43225</t>
+          <t>42060</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62692</t>
+          <t>61721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96260</t>
+          <t>95510</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33979</t>
+          <t>32940</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59058</t>
+          <t>59827</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23183</t>
+          <t>23793</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48284</t>
+          <t>45327</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77036</t>
+          <t>75452</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,52%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27493</t>
+          <t>27017</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51565</t>
+          <t>51149</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16194</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34003</t>
+          <t>33109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60623</t>
+          <t>59880</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64833</t>
+          <t>64594</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91856</t>
+          <t>93008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51632</t>
+          <t>51203</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62589</t>
+          <t>62701</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>119044</t>
+          <t>120162</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>154028</t>
+          <t>153803</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,37%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64219</t>
+          <t>64182</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>91650</t>
+          <t>93861</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13637</t>
+          <t>13941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>69785</t>
+          <t>69723</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>101308</t>
+          <t>101131</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29942</t>
+          <t>29280</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52235</t>
+          <t>52441</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30661</t>
+          <t>30533</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55649</t>
+          <t>54872</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12167</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29950</t>
+          <t>30207</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>12583</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31349</t>
+          <t>30524</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>146998</t>
+          <t>149398</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>188993</t>
+          <t>190555</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>243100</t>
+          <t>241871</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>278288</t>
+          <t>277382</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>398979</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>461633</t>
+          <t>460849</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,18%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>103306</t>
+          <t>102293</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>140772</t>
+          <t>143203</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55641</t>
+          <t>54391</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>85694</t>
+          <t>85328</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>166849</t>
+          <t>167919</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216122</t>
+          <t>217593</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>64088</t>
+          <t>62969</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>97149</t>
+          <t>96382</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18886</t>
+          <t>18866</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38542</t>
+          <t>39328</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>87970</t>
+          <t>88094</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>126294</t>
+          <t>126703</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>95817</t>
+          <t>96771</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134007</t>
+          <t>134809</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18818</t>
+          <t>18426</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>104967</t>
+          <t>104933</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>147224</t>
+          <t>146476</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23869</t>
+          <t>23758</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45475</t>
+          <t>46626</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>98623</t>
+          <t>98030</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>125926</t>
+          <t>125555</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>128742</t>
+          <t>124361</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>167886</t>
+          <t>165895</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -6768,12 +6768,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21298</t>
+          <t>21136</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42721</t>
+          <t>42529</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31129</t>
+          <t>30794</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55109</t>
+          <t>55417</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>58245</t>
+          <t>59008</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>90123</t>
+          <t>90974</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -6881,12 +6881,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26539</t>
+          <t>25969</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>49311</t>
+          <t>50785</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6896,12 +6896,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6916,12 +6916,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13796</t>
+          <t>13798</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6951,12 +6951,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>32380</t>
+          <t>31971</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58600</t>
+          <t>57884</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -6994,12 +6994,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>78024</t>
+          <t>78188</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>107432</t>
+          <t>106459</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7029,12 +7029,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>24122</t>
+          <t>24627</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>44733</t>
+          <t>45387</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7064,12 +7064,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>105539</t>
+          <t>107684</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>144438</t>
+          <t>145130</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>508040</t>
+          <t>506868</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>581427</t>
+          <t>585366</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>687389</t>
+          <t>689849</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>747544</t>
+          <t>751151</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1214686</t>
+          <t>1215815</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1313503</t>
+          <t>1314066</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,72%</t>
         </is>
       </c>
     </row>
@@ -7337,12 +7337,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>328787</t>
+          <t>330127</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>395988</t>
+          <t>398178</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7352,12 +7352,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7372,12 +7372,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>168571</t>
+          <t>166123</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>218958</t>
+          <t>216296</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7407,12 +7407,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>516673</t>
+          <t>515113</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>600616</t>
+          <t>596893</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -7450,12 +7450,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>201614</t>
+          <t>199717</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>259652</t>
+          <t>261724</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7485,12 +7485,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>50442</t>
+          <t>50455</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>80990</t>
+          <t>80242</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7520,12 +7520,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>257927</t>
+          <t>259912</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>323034</t>
+          <t>325165</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -7563,12 +7563,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>248389</t>
+          <t>243643</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>308930</t>
+          <t>304874</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7578,12 +7578,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7598,12 +7598,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>45448</t>
+          <t>45474</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>75365</t>
+          <t>77158</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7633,12 +7633,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>303342</t>
+          <t>299466</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>370961</t>
+          <t>373476</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -8021,32 +8021,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>118930</t>
+          <t>128876</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>105637</t>
+          <t>112225</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>131843</t>
+          <t>144236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8056,32 +8056,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>126600</t>
+          <t>136026</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>117268</t>
+          <t>127243</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>133665</t>
+          <t>142990</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8091,32 +8091,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>245530</t>
+          <t>264903</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>229823</t>
+          <t>247328</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>260344</t>
+          <t>282266</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,2%</t>
         </is>
       </c>
     </row>
@@ -8134,67 +8134,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30370</t>
+          <t>35764</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21321</t>
+          <t>25821</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41591</t>
+          <t>47479</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>12,91%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>23,74%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>19073</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12754</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27115</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>11,85%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>23,12%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18319</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12838</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>27098</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>12,16%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8204,32 +8204,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>48689</t>
+          <t>54837</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38336</t>
+          <t>42422</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62309</t>
+          <t>68499</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,98%</t>
         </is>
       </c>
     </row>
@@ -8247,32 +8247,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24105</t>
+          <t>26379</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>16547</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36310</t>
+          <t>41718</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8282,22 +8282,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8317,32 +8317,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>27538</t>
+          <t>29945</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18061</t>
+          <t>19515</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43117</t>
+          <t>44779</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -8360,32 +8360,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>8948</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8395,32 +8395,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>697</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6324</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8430,32 +8430,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8717</t>
+          <t>11291</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15962</t>
+          <t>20350</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -8473,17 +8473,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8508,17 +8508,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8543,17 +8543,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8590,32 +8590,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>100929</t>
+          <t>104601</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86050</t>
+          <t>90255</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>112653</t>
+          <t>117344</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8625,32 +8625,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>97265</t>
+          <t>103876</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89089</t>
+          <t>95719</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>103183</t>
+          <t>110561</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8660,32 +8660,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>198195</t>
+          <t>208478</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>181439</t>
+          <t>192774</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>213201</t>
+          <t>224181</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>76,91%</t>
         </is>
       </c>
     </row>
@@ -8703,32 +8703,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>34544</t>
+          <t>35592</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25315</t>
+          <t>24261</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48471</t>
+          <t>47179</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8738,32 +8738,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11496</t>
+          <t>12069</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>19306</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8773,32 +8773,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>46040</t>
+          <t>47662</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34602</t>
+          <t>36755</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60913</t>
+          <t>62886</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -8816,32 +8816,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20013</t>
+          <t>22751</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8851,22 +8851,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10437</t>
+          <t>12147</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8886,32 +8886,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>17484</t>
+          <t>19445</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>11834</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>30527</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -8929,32 +8929,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12624</t>
+          <t>13779</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23196</t>
+          <t>24408</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8964,32 +8964,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8999,32 +8999,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>15910</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7616</t>
+          <t>8833</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>28669</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -9042,17 +9042,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9077,17 +9077,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9112,17 +9112,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>41390</t>
+          <t>44972</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>33671</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>129755</t>
+          <t>57315</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9194,32 +9194,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40232</t>
+          <t>44822</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36234</t>
+          <t>40242</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42654</t>
+          <t>47507</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9229,32 +9229,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>81623</t>
+          <t>89793</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21374</t>
+          <t>74872</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>208241</t>
+          <t>103715</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>54,08%</t>
         </is>
       </c>
     </row>
@@ -9272,32 +9272,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47689</t>
+          <t>50951</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>38991</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>149368</t>
+          <t>62835</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9307,32 +9307,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9342,32 +9342,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>51753</t>
+          <t>55188</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>14663</t>
+          <t>42103</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>133911</t>
+          <t>70013</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -9385,32 +9385,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>20905</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>12015</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64044</t>
+          <t>34024</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>637</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9455,32 +9455,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>18917</t>
+          <t>21541</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51573</t>
+          <t>34220</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -9498,32 +9498,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>264946</t>
+          <t>25261</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49734</t>
+          <t>14989</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>342315</t>
+          <t>37832</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9568,32 +9568,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>264946</t>
+          <t>25261</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42533</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>376766</t>
+          <t>39230</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -9611,17 +9611,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>372394</t>
+          <t>142088</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>372394</t>
+          <t>142088</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>372394</t>
+          <t>142088</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9646,17 +9646,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9681,17 +9681,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9728,32 +9728,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>78620</t>
+          <t>89966</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63083</t>
+          <t>73582</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95519</t>
+          <t>108156</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9763,32 +9763,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>139956</t>
+          <t>157091</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>128752</t>
+          <t>144061</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>151370</t>
+          <t>168884</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9798,32 +9798,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>218576</t>
+          <t>247057</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>197771</t>
+          <t>224607</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>241373</t>
+          <t>272380</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>53,2%</t>
         </is>
       </c>
     </row>
@@ -9841,32 +9841,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>59023</t>
+          <t>63054</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44313</t>
+          <t>48544</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>75527</t>
+          <t>78531</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9876,32 +9876,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>34572</t>
+          <t>39323</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25911</t>
+          <t>30135</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45750</t>
+          <t>49801</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9911,32 +9911,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>93595</t>
+          <t>102376</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77797</t>
+          <t>85438</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>112602</t>
+          <t>121250</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -9954,32 +9954,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>60737</t>
+          <t>70207</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48364</t>
+          <t>53549</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>78807</t>
+          <t>85948</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9989,32 +9989,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14317</t>
+          <t>15428</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8868</t>
+          <t>9607</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22872</t>
+          <t>24530</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10024,32 +10024,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>75053</t>
+          <t>85636</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>60209</t>
+          <t>68762</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>93019</t>
+          <t>106767</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -10067,32 +10067,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>60275</t>
+          <t>66847</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46327</t>
+          <t>51929</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76685</t>
+          <t>84307</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10102,32 +10102,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9682</t>
+          <t>10087</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15873</t>
+          <t>16490</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10137,32 +10137,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>69958</t>
+          <t>76934</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55037</t>
+          <t>61431</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88764</t>
+          <t>96763</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -10180,17 +10180,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10215,17 +10215,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>198527</t>
+          <t>221928</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>198527</t>
+          <t>221928</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>198527</t>
+          <t>221928</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10250,17 +10250,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>457182</t>
+          <t>512002</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>457182</t>
+          <t>512002</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>457182</t>
+          <t>512002</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10297,32 +10297,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20746</t>
+          <t>23742</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12935</t>
+          <t>15008</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32419</t>
+          <t>35021</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10332,32 +10332,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>56611</t>
+          <t>66667</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>28388</t>
+          <t>56437</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>74724</t>
+          <t>78549</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10367,32 +10367,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>77357</t>
+          <t>90409</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>53022</t>
+          <t>74224</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>95589</t>
+          <t>107294</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -10410,32 +10410,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>35200</t>
+          <t>41708</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25328</t>
+          <t>29500</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48060</t>
+          <t>55975</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10445,32 +10445,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>67099</t>
+          <t>40816</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39680</t>
+          <t>32209</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112188</t>
+          <t>50504</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10480,32 +10480,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>102299</t>
+          <t>82524</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72409</t>
+          <t>67168</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>161380</t>
+          <t>102994</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -10523,32 +10523,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>17867</t>
+          <t>21017</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10821</t>
+          <t>13415</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27057</t>
+          <t>31312</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10558,32 +10558,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4368</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10593,32 +10593,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>27736</t>
+          <t>32993</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>24227</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37869</t>
+          <t>45110</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -10636,32 +10636,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>58461</t>
+          <t>82283</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>45539</t>
+          <t>67629</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>71375</t>
+          <t>99051</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10671,32 +10671,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>29270</t>
+          <t>35160</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>15418</t>
+          <t>24676</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>41843</t>
+          <t>44693</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10706,32 +10706,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>87731</t>
+          <t>117443</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>58639</t>
+          <t>97972</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>108441</t>
+          <t>137012</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>42,37%</t>
         </is>
       </c>
     </row>
@@ -10749,17 +10749,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10784,17 +10784,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10819,17 +10819,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10866,32 +10866,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>360616</t>
+          <t>392157</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>188940</t>
+          <t>360128</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>481466</t>
+          <t>426749</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10901,32 +10901,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>460666</t>
+          <t>508482</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>372396</t>
+          <t>488990</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>492107</t>
+          <t>530548</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10936,32 +10936,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>821282</t>
+          <t>900639</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>504900</t>
+          <t>858638</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>971517</t>
+          <t>938971</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>55,9%</t>
         </is>
       </c>
     </row>
@@ -10979,32 +10979,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>206826</t>
+          <t>227068</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>105082</t>
+          <t>197261</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>276703</t>
+          <t>256659</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11014,32 +11014,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>135550</t>
+          <t>115519</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>101242</t>
+          <t>99477</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>248063</t>
+          <t>134721</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11049,32 +11049,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>342375</t>
+          <t>342587</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>207777</t>
+          <t>310959</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>424860</t>
+          <t>378185</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -11092,32 +11092,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>133041</t>
+          <t>151420</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>66034</t>
+          <t>127869</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>180150</t>
+          <t>180942</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11127,32 +11127,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>33687</t>
+          <t>38140</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24651</t>
+          <t>28851</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>45487</t>
+          <t>49544</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11162,32 +11162,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>166728</t>
+          <t>189560</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>104925</t>
+          <t>163043</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>204631</t>
+          <t>221339</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -11205,32 +11205,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>402758</t>
+          <t>197118</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>189774</t>
+          <t>168999</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>738814</t>
+          <t>225312</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11240,32 +11240,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>42796</t>
+          <t>49721</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>31775</t>
+          <t>38130</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>55762</t>
+          <t>61909</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11275,32 +11275,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>445554</t>
+          <t>246838</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>221966</t>
+          <t>218702</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>960398</t>
+          <t>282644</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -11318,17 +11318,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1103241</t>
+          <t>967763</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1103241</t>
+          <t>967763</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1103241</t>
+          <t>967763</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11353,17 +11353,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>672699</t>
+          <t>711862</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>672699</t>
+          <t>711862</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>672699</t>
+          <t>711862</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11388,17 +11388,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1775939</t>
+          <t>1679625</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1775939</t>
+          <t>1679625</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1775939</t>
+          <t>1679625</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
